--- a/public/research-sheet-template.xlsx
+++ b/public/research-sheet-template.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G1"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -422,32 +422,9 @@
         <v>Note</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>Example Industries Ltd</v>
-      </c>
-      <c r="B2" t="str">
-        <v>Capital Goods</v>
-      </c>
-      <c r="C2">
-        <v>12345.67</v>
-      </c>
-      <c r="D2" t="str">
-        <v>Tier 1</v>
-      </c>
-      <c r="E2" t="str">
-        <v>EXAMPLE</v>
-      </c>
-      <c r="F2" t="str">
-        <v>Positive</v>
-      </c>
-      <c r="G2" t="str">
-        <v>One-line, plain-English view for this quarter.</v>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/public/research-sheet-template.xlsx
+++ b/public/research-sheet-template.xlsx
@@ -397,34 +397,75 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:O1"/>
+  <cols>
+    <col min="1" max="1" width="12.83203125" customWidth="1"/>
+    <col min="2" max="2" width="14.83203125" customWidth="1"/>
+    <col min="3" max="3" width="18.83203125" customWidth="1"/>
+    <col min="4" max="4" width="18.83203125" customWidth="1"/>
+    <col min="5" max="5" width="22.83203125" customWidth="1"/>
+    <col min="6" max="6" width="22.83203125" customWidth="1"/>
+    <col min="7" max="7" width="16.83203125" customWidth="1"/>
+    <col min="8" max="8" width="16.83203125" customWidth="1"/>
+    <col min="9" max="9" width="16.83203125" customWidth="1"/>
+    <col min="10" max="10" width="16.83203125" customWidth="1"/>
+    <col min="11" max="11" width="12.83203125" customWidth="1"/>
+    <col min="12" max="12" width="12.83203125" customWidth="1"/>
+    <col min="13" max="13" width="18.83203125" customWidth="1"/>
+    <col min="14" max="14" width="12.83203125" customWidth="1"/>
+    <col min="15" max="15" width="12.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>CompanyName</v>
+        <v>Industry</v>
       </c>
       <c r="B1" t="str">
-        <v>Industry</v>
+        <v>Company Name</v>
       </c>
       <c r="C1" t="str">
-        <v>MarketCap</v>
+        <v>YoY Sales Growth</v>
       </c>
       <c r="D1" t="str">
+        <v>QoQ Sales Growth</v>
+      </c>
+      <c r="E1" t="str">
+        <v>YoY Op Profit Growth</v>
+      </c>
+      <c r="F1" t="str">
+        <v>QoQ Op Profit Growth</v>
+      </c>
+      <c r="G1" t="str">
+        <v>YoY EPS Growth</v>
+      </c>
+      <c r="H1" t="str">
+        <v>QoQ EPS Growth</v>
+      </c>
+      <c r="I1" t="str">
+        <v>YoY PAT Growth</v>
+      </c>
+      <c r="J1" t="str">
+        <v>QoQ PAT Growth</v>
+      </c>
+      <c r="K1" t="str">
+        <v>Market Cap</v>
+      </c>
+      <c r="L1" t="str">
         <v>Tier</v>
       </c>
-      <c r="E1" t="str">
+      <c r="M1" t="str">
         <v>TradingView Code</v>
       </c>
-      <c r="F1" t="str">
+      <c r="N1" t="str">
         <v>View</v>
       </c>
-      <c r="G1" t="str">
+      <c r="O1" t="str">
         <v>Note</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/public/research-sheet-template.xlsx
+++ b/public/research-sheet-template.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O1"/>
+  <dimension ref="A1:Y1"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="14.83203125" customWidth="1"/>
@@ -414,6 +414,16 @@
     <col min="13" max="13" width="18.83203125" customWidth="1"/>
     <col min="14" max="14" width="12.83203125" customWidth="1"/>
     <col min="15" max="15" width="12.83203125" customWidth="1"/>
+    <col min="16" max="16" width="12.83203125" customWidth="1"/>
+    <col min="17" max="17" width="12.83203125" customWidth="1"/>
+    <col min="18" max="18" width="14.83203125" customWidth="1"/>
+    <col min="19" max="19" width="12.83203125" customWidth="1"/>
+    <col min="20" max="20" width="19.83203125" customWidth="1"/>
+    <col min="21" max="21" width="19.83203125" customWidth="1"/>
+    <col min="22" max="22" width="21.83203125" customWidth="1"/>
+    <col min="23" max="23" width="21.83203125" customWidth="1"/>
+    <col min="24" max="24" width="21.83203125" customWidth="1"/>
+    <col min="25" max="25" width="21.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -462,10 +472,40 @@
       <c r="O1" t="str">
         <v>Note</v>
       </c>
+      <c r="P1" t="str">
+        <v>EPS TTM</v>
+      </c>
+      <c r="Q1" t="str">
+        <v>5Y Avg P/E</v>
+      </c>
+      <c r="R1" t="str">
+        <v>Industry P/E</v>
+      </c>
+      <c r="S1" t="str">
+        <v>Book Value</v>
+      </c>
+      <c r="T1" t="str">
+        <v>EPS growth 3Years</v>
+      </c>
+      <c r="U1" t="str">
+        <v>EPS growth 5Years</v>
+      </c>
+      <c r="V1" t="str">
+        <v>Sales growth 3Years</v>
+      </c>
+      <c r="W1" t="str">
+        <v>Sales growth 5Years</v>
+      </c>
+      <c r="X1" t="str">
+        <v>EBIDT growth 3Years</v>
+      </c>
+      <c r="Y1" t="str">
+        <v>EBIDT growth 5Years</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:O1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:Y1"/>
   </ignoredErrors>
 </worksheet>
 </file>